--- a/packages/backend/data/A_indicators.xlsx
+++ b/packages/backend/data/A_indicators.xlsx
@@ -568,7 +568,6 @@
           <t>AI_g = \sum | (P_{gi} / \sum P_{g}) - (1/n) | / 2</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>%</t>
@@ -632,7 +631,6 @@
           <t>ASV (ASVI) = (Pixel_wall + Pixel_building + Pixel_fence + Pixel_skyscraper + Pixel_bench + Pixel_streetlight) / Pixel_total</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>%</t>
@@ -696,7 +694,6 @@
           <t>SV = 1.04165 + 2.00634 × WI + 0.49522 × C + 0.23200 × PR</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>%</t>
@@ -760,7 +757,6 @@
           <t>Brightness = (1/(3*M*N)) * sum_{b=1..3} sum_{i=0..N-1} sum_{j=0..M-1} I_bij</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>%</t>
@@ -824,7 +820,6 @@
           <t>L = mean of respondents' Likert ratings (1-5) for the test image relative to the benchmark image; aggregate across N respondents per image.</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>%</t>
@@ -888,7 +883,6 @@
           <t>(Building Pixels / Total Pixels) * 100</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>%</t>
@@ -952,7 +946,6 @@
           <t>Pixel_Ceiling / Total_Pixels</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>%</t>
@@ -1016,7 +1009,6 @@
           <t>Compression Ratio = Size_compressed (JPEG) / Size_original (uncompressed)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>%</t>
@@ -1080,7 +1072,6 @@
           <t>VE = -Sum_i (p_i * log(p_i)) (exact form per Qiu 2023 Supplementary Material SM I; main text only names the metric)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>%</t>
@@ -1144,7 +1135,6 @@
           <t>CR = sum_{i=1..n} M * P_i * log(P_i) where M = sigma_rgyb + 0.3 * mu_rgyb; rg = R - G; yb = 0.5*(R + G) - B; sigma_rgyb = sqrt(sigma_rg^2 + sigma_yb^2</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>%</t>
@@ -1208,7 +1198,6 @@
           <t>CSI = sigma_rgyb + 0.3 * mu_rgyb</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>%</t>
@@ -1272,7 +1261,6 @@
           <t>Pixels_Dirt / Total_Pixels</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>%</t>
@@ -1336,7 +1324,6 @@
           <t>H = − Σ_{i=1}^{n} p_i · ln(p_i) / ln(n)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>%</t>
@@ -1400,7 +1387,6 @@
           <t>M = 1 - ( (N - sqrt( sum_{i=1..5} n_i^2 )) / (N - sqrt(N)) )</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>%</t>
@@ -1464,7 +1450,6 @@
           <t>D = 1 - sum_i [n_i * (n_i - 1)] / [N * (N - 1)]</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>%</t>
@@ -1528,7 +1513,6 @@
           <t>Depth_mean = (1 / (M*N)) * sum_{i,j} D(i,j), where D(i,j) is the predicted depth value at pixel (i,j) of an MxN image</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>%</t>
@@ -1592,7 +1576,6 @@
           <t>EdgeDensity = N(edge pixels) / N(total pixels)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>%</t>
@@ -1656,7 +1639,6 @@
           <t>1 - SVF_S, where SVF_S is the building-only sky view factor from simulation on a building height model (Li et al. 2018, building-only SVF formulation)</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>%</t>
@@ -1672,7 +1654,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1702,6 @@
           <t>DIE_i = [ (1/n)Sum_{k=1..n} B_k + (1/n)Sum_{k=1..n} T_k + (1/n)Sum_{k=1..n} W2_k ] / [ (1/n)Sum_{k=1..n} P1_k + (1/n)Sum_{k=1..n} F_k + (1/n)Sum_{k=1.</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>%</t>
@@ -1784,7 +1765,6 @@
           <t>Enclosure_trees = SVF_S − SVF_P, equivalently (1 − SVF_P) − (1 − SVF_S), where SVF_P is the GSV-based all-inclusive sky view factor and SVF_S is the s</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>%</t>
@@ -1800,7 +1780,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1828,6 @@
           <t>ExG = 2*G - R - B ; per-image vegetation visibility = #{pixels: ExG &gt; Otsu(ExG)} / Pixels_total</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>%</t>
@@ -1912,7 +1891,6 @@
           <t>Category: Sealed vs Open/Railing</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>%</t>
@@ -1976,7 +1954,6 @@
           <t>S_ADI = (SDi - SDj) / SDi ; SDi = sqrt((1/N)*sum_i(Ai - mu_i)^2) ; SDj = sqrt((1/N)*sum_{i!=max}(Ai - mu_w)^2)</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>%</t>
@@ -2040,7 +2017,6 @@
           <t>S_API = sqrt( (1/N) * Sum_{i=1..N} (P_i - mu)^2 )</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>%</t>
@@ -2104,7 +2080,6 @@
           <t>P_ECI = sqrt( (1/N) * sum_j (CV_j - mu_CV)^2 ) / mu_CV ; CV_j = sqrt((1/Mj)*sum_i(Cij - mu_j)^2) / mu_j ; Cij = |idx_i - idx_{i+1}|</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>%</t>
@@ -2168,7 +2143,6 @@
           <t>P_LN = sum_{i=1..N} Unique(Di)</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>%</t>
@@ -2232,7 +2206,6 @@
           <t>P_LV = max_{i in Foreground} Di</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>%</t>
@@ -2296,7 +2269,6 @@
           <t>S_ECI = Pb / (Py + Pb)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>%</t>
@@ -2360,7 +2332,6 @@
           <t>S_ERI = 0.25 * P / sqrt(A)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>%</t>
@@ -2424,7 +2395,6 @@
           <t>S_PSI = sqrt( (1/N) * sum_i ( (0.25*Pi/sqrt(Ai)) - mu )^2 ) / mu , where mu = (1/N) sum_i (0.25*Pi/sqrt(Ai))</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>%</t>
@@ -2488,7 +2458,6 @@
           <t>Pixels_Fence / Pixels_Visible (与其它 VI 元素一致,论文以 0–1 比值表达,可乘 100 得百分比)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>%</t>
@@ -2552,7 +2521,6 @@
           <t>Db = lim (r-&gt;0) [log N(r) / log (1/r)]</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>%</t>
@@ -2616,7 +2584,6 @@
           <t>FreeSpace = (Pixels_grass + Pixels_earth + Pixels_ground + Pixels_outdoor_floor) / Pixels_total</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>%</t>
@@ -2680,7 +2647,6 @@
           <t>Step1: S_c = sum_k p_{c,k} over all images k for category c; Step2: sort p_{c,k} ascending; Step3: q_{c,k} = p_{c,k} / S_c; Step4: G_c = cumulative su</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>%</t>
@@ -2744,7 +2710,6 @@
           <t>vis_texture = - Σ_{i=0..255} Σ_{j=0..255} pg_{ij} * log2 C_{ij}  where C_{ij} is the normalized GLCM entry at offset (Δx, Δy)</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>%</t>
@@ -2808,7 +2773,6 @@
           <t>GCR = Pixel_groundcover / Pixel_total</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>%</t>
@@ -2872,7 +2836,6 @@
           <t>Contrast = Sum_{i=0}^{N-1} Sum_{j=0}^{N-1} (i - j)^2 * P(i, j)</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>%</t>
@@ -2936,7 +2899,6 @@
           <t>(Sum(Green_Pixels) / Sum(Total_Pixels)) * 100</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>%</t>
@@ -3000,7 +2962,6 @@
           <t>GVI_above = N(green_pixels with row &lt; horizon_row) / N(total_pixels);    horizon_row = (H_img / 2) - f_px * tan(pitch_rad);    Place Pulse 1.0 specifi</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>%</t>
@@ -3064,7 +3025,6 @@
           <t>GVI_below = N(green pixels with row &gt;= horizon_row) / N(total pixels); horizon_row = (H_image / 2) + f_px · tan(pitch_rad)  [Li et al. 2015, Eq. 4: Ho</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>%</t>
@@ -3128,7 +3088,6 @@
           <t>GV_band(k) = N(vegetation pixels in latitude band k) / N(total sky-map pixels in latitude band k), for k in {(0,22.5], (22.5,45], (45,67.5], (67.5,90]</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>%</t>
@@ -3192,7 +3151,6 @@
           <t>StdDev(GVI_front, GVI_back, GVI_left, GVI_right)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>%</t>
@@ -3256,7 +3214,6 @@
           <t>Weighted Sum(Greenness, Openness, Enclosure, Walkability, Imageability)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>%</t>
@@ -3320,7 +3277,6 @@
           <t>I_k = (1/n) * sum_{j=1..n} B_jk + (1/n) * sum_{j=1..n} TL_jk + (1/n) * sum_{j=1..n} TS_jk</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>%</t>
@@ -3384,7 +3340,6 @@
           <t>(1/3) * Sum_{b=1..3} sqrt( (1/(M*N)) * Sum_{i,j} (I_bij - I_b_bar)^2 )  where I_b_bar = (1/(M*N)) * Sum I_bij</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>%</t>
@@ -3448,7 +3403,6 @@
           <t>IRI = N_categories_detected / N_categories_total</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>%</t>
@@ -3512,7 +3466,6 @@
           <t>Softmax probability vector output</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>%</t>
@@ -3576,7 +3529,6 @@
           <t>MD = (P_road + P_car + P_bus + P_truck + P_freight_vehicle + P_small_motor_vehicle + P_railway) / P_all</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>%</t>
@@ -3640,7 +3592,6 @@
           <t>Naturalness = arctan( Sum_{c in NaturalSet} A_c / Sum_{c in GreySet} A_c )</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>%</t>
@@ -3704,7 +3655,6 @@
           <t>Ni = [ (1/n) Sum(Tn) + (1/n) Sum(Gn) + (1/n) Sum(W1n) + (1/n) Sum(M1n) + (1/n) Sum(P1n) ] / [ (1/n) Sum(Bn) + (1/n) Sum(W2n) + (1/n) Sum(Rn) + (1/n) S</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>%</t>
@@ -3768,7 +3718,6 @@
           <t>Ni = [(1/n) sum_{i=1..n} (Tn + Gn + W1n + M1n + P1n)] / [(1/n) sum_{i=1..n} (Bn + W2n + Rn + P2n + Fn)]</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>%</t>
@@ -3832,7 +3781,6 @@
           <t>NVGI = G0 / sqrt(R0 * B0)  where  R0 = (R_pixel - R_min)/(R_max - R_min), G0 = (G_pixel - G_min)/(G_max - G_min), B0 = (B_pixel - B_min)/(B_max - B_mi</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>%</t>
@@ -3896,7 +3844,6 @@
           <t>Overhead = (Pixels_tree + Pixels_ceiling + Pixels_canopy) / Pixels_total_topview</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>%</t>
@@ -3912,7 +3859,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3907,6 @@
           <t>PCI = (P_chair + P_toilet + P_bench + P_stool + P_trashcan + P_table + P_armchair + P_light + P_streetlight + P_bulletinboard) / P_all</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>%</t>
@@ -4024,7 +3970,6 @@
           <t>C = Sum_{i=1..n} M * Pi * log(Pi),  with rg = R - G;  yb = 0.5*(R+G) - B;  sigma_rgyb = sqrt(sigma_rg^2 + sigma_yb^2);  mu_rgyb = sqrt(mu_rg^2 + mu_yb</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>%</t>
@@ -4088,7 +4033,6 @@
           <t>Count of instances identified as 'peoples' using Mask R-CNN</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>%</t>
@@ -4152,7 +4096,6 @@
           <t>Level Diversity (richness) = N;  Level Diversity (entropy) = -Sum_{i=1..N} Pi * log2(Pi);  Level Diversity (simpson) = 1 - Sum_{i=1..N} (Pi/P)^2,  whe</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>%</t>
@@ -4216,7 +4159,6 @@
           <t>Pixels_Rider / Total_Pixels</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>%</t>
@@ -4280,7 +4222,6 @@
           <t>Pixel_road / Pixel_total</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>%</t>
@@ -4344,7 +4285,6 @@
           <t>OtherFacilitiesRatio = Pixel_OtherFacilities / Total_Pixels (single aggregated class, not a sum of six sub-classes).</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>%</t>
@@ -4408,7 +4348,6 @@
           <t>SFI = Wn / Rn</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>%</t>
@@ -4472,7 +4411,6 @@
           <t>Per-point: shaded = 1 if sun position overlaps non-sky elements in the segmented fisheye skydome, else 0 (sunlit). Aggregated sunlit ratio: SunlitRati</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>%</t>
@@ -4488,7 +4426,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4474,6 @@
           <t>Pixel_shrub / Pixel_total</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>%</t>
@@ -4600,7 +4537,6 @@
           <t>SPD = P_road + P_path + P_wall + P_stair + P_pillar, where P_x = pixels_x / total_pixels</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>%</t>
@@ -4664,7 +4600,6 @@
           <t>SQI = 1.507*GVI + 0.692*SVI + 0.447*EVI - 2.412*MVI - 0.011*SFI - 0.800*PCI - 0.060*VII + 1.414*ITI - 0.167*CCI + 0.208*SWI + 7.798*VEI - 6.344*IRI</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>%</t>
@@ -4728,7 +4663,6 @@
           <t>SSVF = Pixels_sign_symbol / Pixels_total</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>%</t>
@@ -4792,7 +4726,6 @@
           <t>SVF = (∑_{i=0}^{n} ω · sky(i) / ∑_{i=0}^{n} ω) * 100%</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>%</t>
@@ -4856,7 +4789,6 @@
           <t>|SVF_t - SVF_{t-1}|</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>%</t>
@@ -4872,7 +4804,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4852,6 @@
           <t>SVFdiff = SVFS - SVFP</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>%</t>
@@ -4936,7 +4867,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4915,6 @@
           <t>Terrain_Ratio = N(pixels classified as 'terrain' by SegFormer/Cityscapes) / N(total pixels)</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>%</t>
@@ -5048,7 +4978,6 @@
           <t>TR = (P_traffic_signal + P_sidewalk + P_railway) / P_all</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>%</t>
@@ -5112,7 +5041,6 @@
           <t>TVF = Areat / Areas</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>%</t>
@@ -5176,7 +5104,6 @@
           <t>(Simple) Pixels(Tree) / Total_Pixels  ;  (Hemispherical, Cai et al. 2023) Σ cos(Alti) · Ai · δi,green / Adome,cos</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>%</t>
@@ -5240,7 +5167,6 @@
           <t>K-means Clustering(Gi, Si, Di, Ni)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>%</t>
@@ -5304,7 +5230,6 @@
           <t>Sum(x_perc for x in {sidewalk, escalator, path, stairs, stairway, streetlight, bench, step})</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>%</t>
@@ -5368,7 +5293,6 @@
           <t>1 - ((Tn/GVIn)^2 + (Pn/GVIn)^2 + (Gn/GVIn)^2)</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>%</t>
@@ -5432,7 +5356,6 @@
           <t>(Pixels_car + Pixels_truck + Pixels_bus + Pixels_train + Pixels_motorcycle + Pixels_bicycle) / Total_pixels</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>%</t>
@@ -5496,7 +5419,6 @@
           <t>VE = (Pixels_building + Pixels_wall + Pixels_tree + Pixels_fence) / Pixels_total · 100%   [exact element list to be confirmed against an authoritative</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>%</t>
@@ -5560,7 +5482,6 @@
           <t>Spatialclustering_x = 0.5 * (SUM_i SUM_j x_i x_j) / xperc</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>%</t>
@@ -5624,7 +5545,6 @@
           <t>v_x = GVI_E - GVI_W ; v_y = GVI_N - GVI_S ; |v| = sqrt(v_x^2 + v_y^2) ; theta = atan2(v_y, v_x)  [theta is implicit in the paper but standard]</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>%</t>
@@ -5688,7 +5608,6 @@
           <t>VibrantGreen = N(pixels labelled vegetation AND HSV in healthy-green range) / N(total pixels)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>%</t>
@@ -5752,7 +5671,6 @@
           <t>VII = Pixels_motorised / Pixels_motorway</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
           <t>%</t>
@@ -5816,7 +5734,6 @@
           <t>VQI = Sum_{k in {Safety, Lively, Beautiful, Wealthy, ...}} score_k   (verify against Wang/Ito/Biljecki 2024 Cities 104704)</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
           <t>%</t>
@@ -5880,7 +5797,6 @@
           <t>Pn / (Pn + Rn)</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
           <t>%</t>
@@ -5944,7 +5860,6 @@
           <t>VSD = - Sum_{i=1}^{N} p_i * ln(p_i), where p_i = C_i / C_veg</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
           <t>%</t>
@@ -6008,7 +5923,6 @@
           <t>G_n = Σ_i ( G_i · L_i · D_i^α ) / Σ_i ( L_i · D_i^α )   [source: Ye, Xie, Fang, Jiang &amp; Wang 2019; cannot be verified against the supplied PDF for Lon</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
           <t>%</t>
@@ -6024,7 +5938,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
@@ -6072,7 +5986,6 @@
           <t>Wall Ratio = Pixel_Wall / Total_Pixels</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
           <t>%</t>
@@ -6136,7 +6049,6 @@
           <t>WVI = Pixels_water / Pixels_total</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
           <t>%</t>
@@ -6200,7 +6112,6 @@
           <t>arctan(flora / (grass + non_natural_elements))</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
           <t>%</t>
@@ -6264,7 +6175,6 @@
           <t>W_i = ( (1/4) Σ_{j=1..4} P_j + (1/4) Σ_{j=1..4} F_j ) / ( (1/4) Σ_{j=1..4} Road_j )</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
           <t>%</t>
@@ -6328,7 +6238,6 @@
           <t>VisualWalkability = (Sidewalk_pixels + Fence_pixels) / Road_pixels   (equivalently Pavement_pixels + Fence_pixels / Road_pixels under ADE20K-style lab</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
           <t>%</t>
@@ -6372,7 +6281,6 @@
           <t>SceneRx Metrics Code 总览</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/packages/backend/data/A_indicators.xlsx
+++ b/packages/backend/data/A_indicators.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicators_91" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Indicators_88" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1724,27 +1724,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IND_ENC_TRE</t>
+          <t>IND_EXG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Enclosure by Trees</t>
+          <t>Excess Green Index (Pixel-Color Vegetation Index)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>enclosure</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Enclosure_trees = SVF_S − SVF_P, equivalently (1 − SVF_P) − (1 − SVF_S), where SVF_P is the GSV-based all-inclusive sky view factor and SVF_S is the s</t>
+          <t>ExG = 2*G - R - B ; per-image vegetation visibility = #{pixels: ExG &gt; Otsu(ExG)} / Pixels_total</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sky-view obstruction attributable specifically to tree canopies, computed as the difference between the building-only SVF (simulated from a building/DSM height model) and the all-inclusive SVF (estima</t>
+          <t>A pixel-level RGB-derived index that enhances green vegetation contrast in street-view images. Computed for every pixel from the normalized RGB bands; image-level EXG values can be averaged or thresho</t>
         </is>
       </c>
       <c r="M21" t="n">
@@ -1780,34 +1780,34 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IND_EXG</t>
+          <t>IND_FAC_ENC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Excess Green Index (Pixel-Color Vegetation Index)</t>
+          <t>Facade Enclosure Type</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ExG = 2*G - R - B ; per-image vegetation visibility = #{pixels: ExG &gt; Otsu(ExG)} / Pixels_total</t>
+          <t>Category: Sealed vs Open/Railing</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>A pixel-level RGB-derived index that enhances green vegetation contrast in street-view images. Computed for every pixel from the normalized RGB bands; image-level EXG values can be averaged or thresho</t>
+          <t>Categorical indicator distinguishing between sealed/impervious walls and railing/open facades.</t>
         </is>
       </c>
       <c r="M22" t="n">
@@ -1850,12 +1850,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IND_FAC_ENC</t>
+          <t>IND_S_ADI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Facade Enclosure Type</t>
+          <t>S_ADI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1865,12 +1865,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Category: Sealed vs Open/Railing</t>
+          <t>S_ADI = (SDi - SDj) / SDi ; SDi = sqrt((1/N)*sum_i(Ai - mu_i)^2) ; SDj = sqrt((1/N)*sum_{i!=max}(Ai - mu_w)^2)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Categorical indicator distinguishing between sealed/impervious walls and railing/open facades.</t>
+          <t xml:space="preserve">A relative-relationship metric capturing whether one hole inside the foreground dominates the others in size. Equal to (SDi - SDj)/SDi, where SDi is the standard deviation of all hole areas including </t>
         </is>
       </c>
       <c r="M23" t="n">
@@ -1913,12 +1913,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IND_FG_ADI</t>
+          <t>IND_S_API</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Foreground Largest-Hole Asymmetry Index (S_ADI)</t>
+          <t>S_API</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>S_ADI = (SDi - SDj) / SDi ; SDi = sqrt((1/N)*sum_i(Ai - mu_i)^2) ; SDj = sqrt((1/N)*sum_{i!=max}(Ai - mu_w)^2)</t>
+          <t>S_API = sqrt( (1/N) * Sum_{i=1..N} (P_i - mu)^2 )</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">A relative-relationship metric capturing whether one hole inside the foreground dominates the others in size. Equal to (SDi - SDj)/SDi, where SDi is the standard deviation of all hole areas including </t>
+          <t>A distributional-trend metric describing the lateral asymmetry of the foreground outline relative to the vertical midline of the field of view, computed as the standard deviation of the per-row midpoi</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1976,12 +1976,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IND_FG_API</t>
+          <t>IND_P_ECI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Foreground Asymmetry / Profile Index (S_API)</t>
+          <t>P_ECI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>S_API = sqrt( (1/N) * Sum_{i=1..N} (P_i - mu)^2 )</t>
+          <t>P_ECI = sqrt( (1/N) * sum_j (CV_j - mu_CV)^2 ) / mu_CV ; CV_j = sqrt((1/Mj)*sum_i(Cij - mu_j)^2) / mu_j ; Cij = |idx_i - idx_{i+1}|</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>A distributional-trend metric describing the lateral asymmetry of the foreground outline relative to the vertical midline of the field of view, computed as the standard deviation of the per-row midpoi</t>
+          <t>A distributional trend metric measuring how smoothly depth values transition across the foreground. Computed as the coefficient of variation of the per-row/column coefficients of variation of the abso</t>
         </is>
       </c>
       <c r="M25" t="n">
@@ -2039,12 +2039,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IND_FG_DEPTH_ECI</t>
+          <t>IND_P_LN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Foreground Depth Continuity Index (P_ECI)</t>
+          <t>P_LN</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>P_ECI = sqrt( (1/N) * sum_j (CV_j - mu_CV)^2 ) / mu_CV ; CV_j = sqrt((1/Mj)*sum_i(Cij - mu_j)^2) / mu_j ; Cij = |idx_i - idx_{i+1}|</t>
+          <t>P_LN = sum_{i=1..N} Unique(Di)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>A distributional trend metric measuring how smoothly depth values transition across the foreground. Computed as the coefficient of variation of the per-row/column coefficients of variation of the abso</t>
+          <t>An absolute-value position metric: the count of unique non-repeating depth values among pixels in the foreground, representing the vertical depth extent (range) of the foreground.</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -2102,12 +2102,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IND_FG_DEPTH_LN</t>
+          <t>IND_P_LV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Foreground Vertical Depth Length (P_LN)</t>
+          <t>P_LV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>P_LN = sum_{i=1..N} Unique(Di)</t>
+          <t>P_LV = max_{i in Foreground} Di</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>An absolute-value position metric: the count of unique non-repeating depth values among pixels in the foreground, representing the vertical depth extent (range) of the foreground.</t>
+          <t xml:space="preserve">An absolute-value position metric: the maximum depth value across all pixels in the foreground, derived from monocular depth estimation grayscale (1-256). High values mean the foreground starts close </t>
         </is>
       </c>
       <c r="M27" t="n">
@@ -2165,12 +2165,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IND_FG_DEPTH_LV</t>
+          <t>IND_S_ECI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Foreground Maximum Depth Value (P_LV)</t>
+          <t>S_ECI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>P_LV = max_{i in Foreground} Di</t>
+          <t>S_ECI = Pb / (Py + Pb)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">An absolute-value position metric: the maximum depth value across all pixels in the foreground, derived from monocular depth estimation grayscale (1-256). High values mean the foreground starts close </t>
+          <t>Measures how distinct the foreground is from its surrounding elements by checking element-label consistency of the 8-neighborhood for each pixel on the foreground outline. Values near 0 indicate the f</t>
         </is>
       </c>
       <c r="M28" t="n">
@@ -2228,12 +2228,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IND_FG_ECI</t>
+          <t>IND_S_ERI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Foreground Edge Contrast Index (S_ECI)</t>
+          <t>S_ERI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>S_ECI = Pb / (Py + Pb)</t>
+          <t>S_ERI = 0.25 * P / sqrt(A)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Measures how distinct the foreground is from its surrounding elements by checking element-label consistency of the 8-neighborhood for each pixel on the foreground outline. Values near 0 indicate the f</t>
+          <t>A shape metric describing the irregularity of the foreground outline derived from semantic-segmented street/scenic images, based on the isoperimetric inequality. Compares the perimeter of the foregrou</t>
         </is>
       </c>
       <c r="M29" t="n">
@@ -2291,12 +2291,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IND_FG_ERI</t>
+          <t>IND_S_PSI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Foreground Edge Roughness Index (S_ERI)</t>
+          <t>S_PSI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>S_ERI = 0.25 * P / sqrt(A)</t>
+          <t>S_PSI = sqrt( (1/N) * sum_i ( (0.25*Pi/sqrt(Ai)) - mu )^2 ) / mu , where mu = (1/N) sum_i (0.25*Pi/sqrt(Ai))</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>A shape metric describing the irregularity of the foreground outline derived from semantic-segmented street/scenic images, based on the isoperimetric inequality. Compares the perimeter of the foregrou</t>
+          <t>A distributional trend metric describing how similar in shape the multiple holes (open patches inside the foreground) are. Computed as the coefficient of variation of the perimeter-area shape descript</t>
         </is>
       </c>
       <c r="M30" t="n">
@@ -2354,27 +2354,27 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IND_FG_PSI</t>
+          <t>IND_FNC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Foreground Hole-Shape Similarity Index (S_PSI)</t>
+          <t>Fence Ratio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2384,15 +2384,15 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>S_PSI = sqrt( (1/N) * sum_i ( (0.25*Pi/sqrt(Ai)) - mu )^2 ) / mu , where mu = (1/N) sum_i (0.25*Pi/sqrt(Ai))</t>
+          <t>Pixels_Fence / Pixels_Visible (与其它 VI 元素一致,论文以 0–1 比值表达,可乘 100 得百分比)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>A distributional trend metric describing how similar in shape the multiple holes (open patches inside the foreground) are. Computed as the coefficient of variation of the perimeter-area shape descript</t>
+          <t>IND_FNC (Fence Ratio) 属于 Zhang et al. (2021) 提出的 view index (VI) 体系中的物理感知指标之一,定义为街景图中 Fence (栅栏) 类别像素占可视区域像素的比例。论文采用基于 COCO Panoptic Segmentation 训练的 Panoptic-FPN,将每张街景图解析为 17 类主要物理元素,Fence 为其中一类。</t>
         </is>
       </c>
       <c r="M31" t="n">
@@ -2417,17 +2417,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IND_FNC</t>
+          <t>IND_FRD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fence Ratio</t>
+          <t>Fractal Dimension</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2447,29 +2447,29 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Db = lim (r-&gt;0) [log N(r) / log (1/r)]</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>IND_FRD is a quantitative measure of morphological complexity and roughness, derived from fractal geometry. In visual landscape analysis, it assesses the texture and edge complexity of skylines or veg</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>2</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Pixels_Fence / Pixels_Visible (与其它 VI 元素一致,论文以 0–1 比值表达,可乘 100 得百分比)</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>IND_FNC (Fence Ratio) 属于 Zhang et al. (2021) 提出的 view index (VI) 体系中的物理感知指标之一,定义为街景图中 Fence (栅栏) 类别像素占可视区域像素的比例。论文采用基于 COCO Panoptic Segmentation 训练的 Panoptic-FPN,将每张街景图解析为 17 类主要物理元素,Fence 为其中一类。</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2480,27 +2480,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IND_FRD</t>
+          <t>IND_FREE_SPC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fractal Dimension</t>
+          <t>Free Space Ratio</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Db = lim (r-&gt;0) [log N(r) / log (1/r)]</t>
+          <t>FreeSpace = (Pixels_grass + Pixels_earth + Pixels_ground + Pixels_outdoor_floor) / Pixels_total</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2528,11 +2528,11 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>IND_FRD is a quantitative measure of morphological complexity and roughness, derived from fractal geometry. In visual landscape analysis, it assesses the texture and edge complexity of skylines or veg</t>
+          <t>Pixel-area proportion of surfaces available for free (non-vehicular) activity, summing semantic classes such as grass, earth, ground and outdoor floor; designed to operationalize the 'cohesive / conne</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2543,12 +2543,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IND_FREE_SPC</t>
+          <t>IND_GIN</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Free Space Ratio</t>
+          <t>Gini Index</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>FreeSpace = (Pixels_grass + Pixels_earth + Pixels_ground + Pixels_outdoor_floor) / Pixels_total</t>
+          <t>Step1: S_c = sum_k p_{c,k} over all images k for category c; Step2: sort p_{c,k} ascending; Step3: q_{c,k} = p_{c,k} / S_c; Step4: G_c = cumulative su</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2591,11 +2591,11 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Pixel-area proportion of surfaces available for free (non-vehicular) activity, summing semantic classes such as grass, earth, ground and outdoor floor; designed to operationalize the 'cohesive / conne</t>
+          <t>Gini Index (per landscape category): a 4-step diversity statistic on the across-image distribution of a single semantic-segmentation category's pixel-proportion values within an urban neighborhood. La</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2606,22 +2606,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IND_GIN</t>
+          <t>IND_GLCM_ENT</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gini Index</t>
+          <t>Texture Entropy (GLCM Entropy)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Step1: S_c = sum_k p_{c,k} over all images k for category c; Step2: sort p_{c,k} ascending; Step3: q_{c,k} = p_{c,k} / S_c; Step4: G_c = cumulative su</t>
+          <t>vis_texture = - Σ_{i=0..255} Σ_{j=0..255} pg_{ij} * log2 C_{ij}  where C_{ij} is the normalized GLCM entry at offset (Δx, Δy)</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2654,11 +2654,11 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Gini Index (per landscape category): a 4-step diversity statistic on the across-image distribution of a single semantic-segmentation category's pixel-proportion values within an urban neighborhood. La</t>
+          <t>Gray-Level Co-occurrence Matrix entropy applied to a street-view panorama, measuring textural non-uniformity / complexity of recurring local visual patterns.</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2669,27 +2669,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IND_GLCM_ENT</t>
+          <t>IND_GRC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Texture Entropy (GLCM Entropy)</t>
+          <t>Ground Cover Ratio</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2699,15 +2699,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>vis_texture = - Σ_{i=0..255} Σ_{j=0..255} pg_{ij} * log2 C_{ij}  where C_{ij} is the normalized GLCM entry at offset (Δx, Δy)</t>
+          <t>GCR = Pixel_groundcover / Pixel_total</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Gray-Level Co-occurrence Matrix entropy applied to a street-view panorama, measuring textural non-uniformity / complexity of recurring local visual patterns.</t>
+          <t>Proportion of panoramic / street-view image pixels classified as ground cover (open lawn / low herbaceous vegetation) by semantic segmentation. In Zhao &amp; Lin (2024) ground cover is one of 13 visual-el</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -2732,12 +2732,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IND_GRC</t>
+          <t>IND_GRC_CON</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ground Cover Ratio</t>
+          <t>Grayscale Contrast (GLCM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2762,15 +2762,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>GCR = Pixel_groundcover / Pixel_total</t>
+          <t>Contrast = Sum_{i=0}^{N-1} Sum_{j=0}^{N-1} (i - j)^2 * P(i, j)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Proportion of panoramic / street-view image pixels classified as ground cover (open lawn / low herbaceous vegetation) by semantic segmentation. In Zhao &amp; Lin (2024) ground cover is one of 13 visual-el</t>
+          <t>Grayscale Contrast (GLCM) is a texture-based image-complexity metric computed from the Gray Level Co-occurrence Matrix (GLCM) of a streetscape image. It captures local variations in grayscale intensit</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2795,12 +2795,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IND_GRC_CON</t>
+          <t>IND_GVI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Grayscale Contrast (GLCM)</t>
+          <t>Green View Index</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2825,15 +2825,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Contrast = Sum_{i=0}^{N-1} Sum_{j=0}^{N-1} (i - j)^2 * P(i, j)</t>
+          <t>(Sum(Green_Pixels) / Sum(Total_Pixels)) * 100</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2843,11 +2843,11 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Grayscale Contrast (GLCM) is a texture-based image-complexity metric computed from the Gray Level Co-occurrence Matrix (GLCM) of a streetscape image. It captures local variations in grayscale intensit</t>
+          <t>Proportion of green vegetation pixels in street-level imagery</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2858,12 +2858,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IND_GVI</t>
+          <t>IND_GVI_HOR_ABV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Green View Index</t>
+          <t>Above-Horizon Green View Index</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2892,11 +2892,11 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>(Sum(Green_Pixels) / Sum(Total_Pixels)) * 100</t>
+          <t>GVI_above = N(green_pixels with row &lt; horizon_row) / N(total_pixels);    horizon_row = (H_img / 2) - f_px * tan(pitch_rad);    Place Pulse 1.0 specifi</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Proportion of green vegetation pixels in street-level imagery</t>
+          <t>The percentage of green-vegetation pixels located above the camera 2.5 m horizon line (i.e. vegetation higher than the camera height of ~2.5 m) within a street-view image. It captures non-view-obstruc</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2921,12 +2921,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IND_GVI_HOR_ABV</t>
+          <t>IND_GVI_HOR_BLW</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Above-Horizon Green View Index</t>
+          <t>Below-Horizon Green View Index</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>GVI_above = N(green_pixels with row &lt; horizon_row) / N(total_pixels);    horizon_row = (H_img / 2) - f_px * tan(pitch_rad);    Place Pulse 1.0 specifi</t>
+          <t>GVI_below = N(green pixels with row &gt;= horizon_row) / N(total pixels); horizon_row = (H_image / 2) + f_px · tan(pitch_rad)  [Li et al. 2015, Eq. 4: Ho</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>The percentage of green-vegetation pixels located above the camera 2.5 m horizon line (i.e. vegetation higher than the camera height of ~2.5 m) within a street-view image. It captures non-view-obstruc</t>
+          <t>Percentage of green-vegetation pixels located below the camera's 2.5 m horizon line in a GSV image — these pixels correspond to vegetation lower than 2.5 m (lawns, shrubs, small trees), which Li et al</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2984,27 +2984,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IND_GVI_HOR_BLW</t>
+          <t>IND_GVI_LATBAND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Below-Horizon Green View Index</t>
+          <t>Green Visibility by Latitude Band (Zenith-Angle Banded GVI)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>GVI_below = N(green pixels with row &gt;= horizon_row) / N(total pixels); horizon_row = (H_image / 2) + f_px · tan(pitch_rad)  [Li et al. 2015, Eq. 4: Ho</t>
+          <t>GV_band(k) = N(vegetation pixels in latitude band k) / N(total sky-map pixels in latitude band k), for k in {(0,22.5], (22.5,45], (45,67.5], (67.5,90]</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Percentage of green-vegetation pixels located below the camera's 2.5 m horizon line in a GSV image — these pixels correspond to vegetation lower than 2.5 m (lawns, shrubs, small trees), which Li et al</t>
+          <t>Green visibility computed inside each of FOUR latitude (zenith-angle) bands (0-22.5 deg, 22.5-45.0 deg, 45.0-67.5 deg, 67.5-90.0 deg) on a sky-map (orthographic-projection fisheye) image obtained by t</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -3047,22 +3047,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IND_GVI_LATBAND</t>
+          <t>IND_GVI_VAR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Green Visibility by Latitude Band (Zenith-Angle Banded GVI)</t>
+          <t>GVI Variation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>GV_band(k) = N(vegetation pixels in latitude band k) / N(total sky-map pixels in latitude band k), for k in {(0,22.5], (22.5,45], (45,67.5], (67.5,90]</t>
+          <t>StdDev(GVI_front, GVI_back, GVI_left, GVI_right)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Green visibility computed inside each of FOUR latitude (zenith-angle) bands (0-22.5 deg, 22.5-45.0 deg, 45.0-67.5 deg, 67.5-90.0 deg) on a sky-map (orthographic-projection fisheye) image obtained by t</t>
+          <t>Standard deviation of Green View Index across the four horizontal views, indicating heterogeneity of greenery.</t>
         </is>
       </c>
       <c r="M42" t="n">
@@ -3110,17 +3110,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IND_GVI_VAR</t>
+          <t>IND_HPS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GVI Variation</t>
+          <t>Human Perception Score</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>StdDev(GVI_front, GVI_back, GVI_left, GVI_right)</t>
+          <t>Weighted Sum(Greenness, Openness, Enclosure, Walkability, Imageability)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3158,11 +3158,11 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Standard deviation of Green View Index across the four horizontal views, indicating heterogeneity of greenery.</t>
+          <t>A composite score derived from Greenness, Openness, Enclosure, Walkability, and Imageability using Entropy Weighting Method.</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -3173,12 +3173,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IND_HPS</t>
+          <t>IND_IMG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Human Perception Score</t>
+          <t>Imageability (Streetscape)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Weighted Sum(Greenness, Openness, Enclosure, Walkability, Imageability)</t>
+          <t>I_k = (1/n) * sum_{j=1..n} B_jk + (1/n) * sum_{j=1..n} TL_jk + (1/n) * sum_{j=1..n} TS_jk</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3221,11 +3221,11 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>A composite score derived from Greenness, Openness, Enclosure, Walkability, and Imageability using Entropy Weighting Method.</t>
+          <t xml:space="preserve">Average pixel proportion across n images of building, traffic-light, and traffic-sign elements at a sampling point. Operationalises Lynch's 'imageability' from street view images as the prevalence of </t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -3236,22 +3236,22 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IND_IMG</t>
+          <t>IND_IMG_CON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Imageability (Streetscape)</t>
+          <t>Image Contrast</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>I_k = (1/n) * sum_{j=1..n} B_jk + (1/n) * sum_{j=1..n} TL_jk + (1/n) * sum_{j=1..n} TS_jk</t>
+          <t>(1/3) * Sum_{b=1..3} sqrt( (1/(M*N)) * Sum_{i,j} (I_bij - I_b_bar)^2 )  where I_b_bar = (1/(M*N)) * Sum I_bij</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Average pixel proportion across n images of building, traffic-light, and traffic-sign elements at a sampling point. Operationalises Lynch's 'imageability' from street view images as the prevalence of </t>
+          <t>The difference in luminance or color that makes an object distinguishable, measured via Root Mean Square Contrast.</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -3299,12 +3299,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IND_IMG_CON</t>
+          <t>IND_IRI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Image Contrast</t>
+          <t>Interfacial Richness Index</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>(1/3) * Sum_{b=1..3} sqrt( (1/(M*N)) * Sum_{i,j} (I_bij - I_b_bar)^2 )  where I_b_bar = (1/(M*N)) * Sum I_bij</t>
+          <t>IRI = N_categories_detected / N_categories_total</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>The difference in luminance or color that makes an object distinguishable, measured via Root Mean Square Contrast.</t>
+          <t>Number of distinct semantic categories detected in a street-view image divided by the total number of categories supported by the segmentation model; measures categorical richness of the streetscape i</t>
         </is>
       </c>
       <c r="M46" t="n">
@@ -3362,27 +3362,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IND_IRI</t>
+          <t>IND_LEG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Interfacial Richness Index</t>
+          <t>Legibility Index</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>deep_learning</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>IRI = N_categories_detected / N_categories_total</t>
+          <t>Softmax probability vector output</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3410,11 +3410,11 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Number of distinct semantic categories detected in a street-view image divided by the total number of categories supported by the segmentation model; measures categorical richness of the streetscape i</t>
+          <t>A measure of the extent to which a space can be easily identified and organized in a coherent pattern, often quantified by the confidence score of a deep learning classification model.</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -3425,27 +3425,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IND_LEG</t>
+          <t>IND_MTD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Legibility Index</t>
+          <t>Motorization Degree</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>deep_learning</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Softmax probability vector output</t>
+          <t>MD = (P_road + P_car + P_bus + P_truck + P_freight_vehicle + P_small_motor_vehicle + P_railway) / P_all</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3473,11 +3473,11 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>A measure of the extent to which a space can be easily identified and organized in a coherent pattern, often quantified by the confidence score of a deep learning classification model.</t>
+          <t>Sum of pixel proportions of all motor-traffic-related elements (road surface plus all vehicle classes plus railway) in a street view image. Captures how dominant motor traffic infrastructure and vehic</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -3488,27 +3488,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IND_MTD</t>
+          <t>IND_NAT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Motorization Degree</t>
+          <t>Naturalness Index</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>deep_learning</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MD = (P_road + P_car + P_bus + P_truck + P_freight_vehicle + P_small_motor_vehicle + P_railway) / P_all</t>
+          <t>Naturalness = arctan( Sum_{c in NaturalSet} A_c / Sum_{c in GreySet} A_c )</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3536,11 +3536,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sum of pixel proportions of all motor-traffic-related elements (road surface plus all vehicle classes plus railway) in a street view image. Captures how dominant motor traffic infrastructure and vehic</t>
+          <t>Naturalness = arctan( sum of pixel-area proportions of natural semantic classes (e.g., tree, grass, plant/flora, palm, water, rock, mountain, animal) divided by sum of pixel-area proportions of grey/a</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -3551,27 +3551,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IND_NAT</t>
+          <t>IND_NAT_ART</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Naturalness Index</t>
+          <t>Natural-to-Artificial Element Ratio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>deep_learning</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Naturalness = arctan( Sum_{c in NaturalSet} A_c / Sum_{c in GreySet} A_c )</t>
+          <t>Ni = [ (1/n) Sum(Tn) + (1/n) Sum(Gn) + (1/n) Sum(W1n) + (1/n) Sum(M1n) + (1/n) Sum(P1n) ] / [ (1/n) Sum(Bn) + (1/n) Sum(W2n) + (1/n) Sum(Rn) + (1/n) S</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Naturalness = arctan( sum of pixel-area proportions of natural semantic classes (e.g., tree, grass, plant/flora, palm, water, rock, mountain, animal) divided by sum of pixel-area proportions of grey/a</t>
+          <t>Ratio of the average proportion of natural-element pixels (trees, grass, water, mountains, plants) to the average proportion of artificial-element pixels (buildings, walls, roads, pavement, fences) ac</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3614,12 +3614,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IND_NAT_ART</t>
+          <t>IND_NAT_LND</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Natural-to-Artificial Element Ratio</t>
+          <t>Natural Landscape Index</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3648,11 +3648,11 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Ni = [ (1/n) Sum(Tn) + (1/n) Sum(Gn) + (1/n) Sum(W1n) + (1/n) Sum(M1n) + (1/n) Sum(P1n) ] / [ (1/n) Sum(Bn) + (1/n) Sum(W2n) + (1/n) Sum(Rn) + (1/n) S</t>
+          <t>Ni = [(1/n) sum_{i=1..n} (Tn + Gn + W1n + M1n + P1n)] / [(1/n) sum_{i=1..n} (Bn + W2n + Rn + P2n + Fn)]</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Ratio of the average proportion of natural-element pixels (trees, grass, water, mountains, plants) to the average proportion of artificial-element pixels (buildings, walls, roads, pavement, fences) ac</t>
+          <t>Naturalness (Ni): the ratio of the sum of percentages of natural-element pixels (trees, grass, water, mountains, plants) to the sum of percentages of artificial-element pixels (buildings, walls, roads</t>
         </is>
       </c>
       <c r="M51" t="n">
@@ -3677,12 +3677,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IND_NAT_LND</t>
+          <t>IND_NVGI</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Natural Landscape Index</t>
+          <t>Normalized Vegetation Greenery Index (RGB-based)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3707,15 +3707,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Ni = [(1/n) sum_{i=1..n} (Tn + Gn + W1n + M1n + P1n)] / [(1/n) sum_{i=1..n} (Bn + W2n + Rn + P2n + Fn)]</t>
+          <t>NVGI = G0 / sqrt(R0 * B0)  where  R0 = (R_pixel - R_min)/(R_max - R_min), G0 = (G_pixel - G_min)/(G_max - G_min), B0 = (B_pixel - B_min)/(B_max - B_mi</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Naturalness (Ni): the ratio of the sum of percentages of natural-element pixels (trees, grass, water, mountains, plants) to the sum of percentages of artificial-element pixels (buildings, walls, roads</t>
+          <t>A normalized RGB-based pixel index designed to substitute for satellite NDVI when only RGB street-view data is available. Higher NVGI separates green vegetation from other features in BSV/GSV imagery.</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3740,12 +3740,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IND_NVGI</t>
+          <t>IND_OVH_SHL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Normalized Vegetation Greenery Index (RGB-based)</t>
+          <t>Overhead Shelter Ratio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>NVGI = G0 / sqrt(R0 * B0)  where  R0 = (R_pixel - R_min)/(R_max - R_min), G0 = (G_pixel - G_min)/(G_max - G_min), B0 = (B_pixel - B_min)/(B_max - B_mi</t>
+          <t>Overhead = (Pixels_tree + Pixels_ceiling + Pixels_canopy) / Pixels_total_topview</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>A normalized RGB-based pixel index designed to substitute for satellite NDVI when only RGB street-view data is available. Higher NVGI separates green vegetation from other features in BSV/GSV imagery.</t>
+          <t xml:space="preserve">Pixel-area proportion of overhead-sheltering elements (trees, ceiling, canopy) in the TOP VIEW of a panorama (i.e. the bird's-eye sub-image of a 360° GSV panorama, not the upright street-view image); </t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3796,19 +3796,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IND_OVH_SHL</t>
+          <t>IND_PCI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Overhead Shelter Ratio</t>
+          <t>Public-Facility Convenience Index</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Overhead = (Pixels_tree + Pixels_ceiling + Pixels_canopy) / Pixels_total_topview</t>
+          <t>PCI = (P_chair + P_toilet + P_bench + P_stool + P_trashcan + P_table + P_armchair + P_light + P_streetlight + P_bulletinboard) / P_all</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixel-area proportion of overhead-sheltering elements (trees, ceiling, canopy) in the TOP VIEW of a panorama (i.e. the bird's-eye sub-image of a 360° GSV panorama, not the upright street-view image); </t>
+          <t>Public-Facility Convenience Index (PCI):街景图中 10 类公共服务设施像素之和与图像总像素的比值,反映街区便民设施基础设施水平。</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3859,19 +3859,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IND_PCI</t>
+          <t>IND_PED_CNT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Public-Facility Convenience Index</t>
+          <t>Pedestrian Count</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>deep_learning</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PCI = (P_chair + P_toilet + P_bench + P_stool + P_trashcan + P_table + P_armchair + P_light + P_streetlight + P_bulletinboard) / P_all</t>
+          <t>Count of instances identified as 'peoples' using Mask R-CNN</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Public-Facility Convenience Index (PCI):街景图中 10 类公共服务设施像素之和与图像总像素的比值,反映街区便民设施基础设施水平。</t>
+          <t>The absolute count of people or pedestrians identified within the visual scene (SVI).</t>
         </is>
       </c>
       <c r="M55" t="n">
@@ -3929,12 +3929,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IND_PCR</t>
+          <t>IND_RID_RAT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Plant Color Richness</t>
+          <t>Rider Ratio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3959,15 +3959,15 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>C = Sum_{i=1..n} M * Pi * log(Pi),  with rg = R - G;  yb = 0.5*(R+G) - B;  sigma_rgyb = sqrt(sigma_rg^2 + sigma_yb^2);  mu_rgyb = sqrt(mu_rg^2 + mu_yb</t>
+          <t>Pixels_Rider / Total_Pixels</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>An entropy-based color richness index applied specifically to plant pixels (after extracting plant regions from semantic segmentation). It multiplies a color-saturation factor M (sigma_rgyb + 0.3*mu_r</t>
+          <t>The proportion of pixels in a street view image representing riders (persons on vehicles such as bicycles or motorcycles).</t>
         </is>
       </c>
       <c r="M56" t="n">
@@ -3992,12 +3992,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IND_PED_CNT</t>
+          <t>IND_RVI</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Pedestrian Count</t>
+          <t>Road View Index</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>deep_learning</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4022,15 +4022,15 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Count of instances identified as 'peoples' using Mask R-CNN</t>
+          <t>Pixel_road / Pixel_total</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -4040,11 +4040,11 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>The absolute count of people or pedestrians identified within the visual scene (SVI).</t>
+          <t>Proportion of road surface visible</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -4055,12 +4055,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IND_PLD</t>
+          <t>IND_SEF</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Plant Level Diversity</t>
+          <t>Service Facility</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4085,15 +4085,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Level Diversity (richness) = N;  Level Diversity (entropy) = -Sum_{i=1..N} Pi * log2(Pi);  Level Diversity (simpson) = 1 - Sum_{i=1..N} (Pi/P)^2,  whe</t>
+          <t>OtherFacilitiesRatio = Pixel_OtherFacilities / Total_Pixels (single aggregated class, not a sum of six sub-classes).</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Diversity of plant landscape strata (grass, flowers, shrubs/plants, trees) seen in a street view. Operationalized as the count, Shannon-entropy, or Simpson form computed over the four vertical-vegetat</t>
+          <t>If the indicator is to be retained against this paper, redefine as: 'Other Facilities Ratio' = pixel proportion of the aggregate 'Other Facilities' label (tables, chairs, streetlights, traffic lights,</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -4118,17 +4118,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IND_RID_RAT</t>
+          <t>IND_SFI</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rider Ratio</t>
+          <t>Spatial Feasibility Index</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4148,15 +4148,15 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Pixels_Rider / Total_Pixels</t>
+          <t>SFI = Wn / Rn</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The proportion of pixels in a street view image representing riders (persons on vehicles such as bicycles or motorcycles).</t>
+          <t>The ratio of sidewalk pixels to car lane pixels in a street view image, representing pedestrian space priority.</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -4181,17 +4181,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IND_RVI</t>
+          <t>IND_SHA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Road View Index</t>
+          <t>Shade Coverage</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4211,15 +4211,15 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Pixel_road / Pixel_total</t>
+          <t>Per-point: shaded = 1 if sun position overlaps non-sky elements in the segmented fisheye skydome, else 0 (sunlit). Aggregated sunlit ratio: SunlitRati</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4229,27 +4229,27 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Proportion of road surface visible</t>
+          <t>IND_SHA quantifies shade exposure along a street as a sun-path-derived binary status (sunlit=1 / shaded=0) at each sampling point, obtained by overlaying the sun's azimuth/elevation track on a segment</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IND_SEF</t>
+          <t>IND_SHR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Service Facility</t>
+          <t>Shrub Ratio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4278,11 +4278,11 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OtherFacilitiesRatio = Pixel_OtherFacilities / Total_Pixels (single aggregated class, not a sum of six sub-classes).</t>
+          <t>Pixel_shrub / Pixel_total</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4292,11 +4292,11 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>If the indicator is to be retained against this paper, redefine as: 'Other Facilities Ratio' = pixel proportion of the aggregate 'Other Facilities' label (tables, chairs, streetlights, traffic lights,</t>
+          <t>Proportion of shrub vegetation</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
@@ -4307,12 +4307,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IND_SFI</t>
+          <t>IND_SPD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spatial Feasibility Index</t>
+          <t>Spatial Division</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>SFI = Wn / Rn</t>
+          <t>SPD = P_road + P_path + P_wall + P_stair + P_pillar, where P_x = pixels_x / total_pixels</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The ratio of sidewalk pixels to car lane pixels in a street view image, representing pedestrian space priority.</t>
+          <t>Sum of the area proportions of elements that divide a coherent and integral activity space within a street-view image; in Zhang et al. (2023) the dividing elements are road, path, wall, stair, and pil</t>
         </is>
       </c>
       <c r="M62" t="n">
@@ -4370,17 +4370,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IND_SHA</t>
+          <t>IND_SQI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Shade Coverage</t>
+          <t>Street Quality Index (Composite)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Per-point: shaded = 1 if sun position overlaps non-sky elements in the segmented fisheye skydome, else 0 (sunlit). Aggregated sunlit ratio: SunlitRati</t>
+          <t>SQI = 1.507*GVI + 0.692*SVI + 0.447*EVI - 2.412*MVI - 0.011*SFI - 0.800*PCI - 0.060*VII + 1.414*ITI - 0.167*CCI + 0.208*SWI + 7.798*VEI - 6.344*IRI</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>IND_SHA quantifies shade exposure along a street as a sun-path-derived binary status (sunlit=1 / shaded=0) at each sampling point, obtained by overlaying the sun's azimuth/elevation track on a segment</t>
+          <t>A composite index measuring the overall spatial quality of an urban street based on visual indicators including green view, enclosure, motorization, and openness, derived via AHP weights.</t>
         </is>
       </c>
       <c r="M63" t="n">
@@ -4426,19 +4426,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IND_SHR</t>
+          <t>IND_SSVF</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Shrub Ratio</t>
+          <t>Sign Symbol View Factor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4467,11 +4467,11 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Pixel_shrub / Pixel_total</t>
+          <t>SSVF = Pixels_sign_symbol / Pixels_total</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4481,11 +4481,11 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Proportion of shrub vegetation</t>
+          <t xml:space="preserve">Sign Symbol View Factor (SSVF): the proportion of pixels classified as 'sign symbol' in a street-view image obtained via semantic segmentation, used as a view-factor measure of pedestrian exposure to </t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
@@ -4496,17 +4496,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IND_SPD</t>
+          <t>IND_SVF</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Spatial Division</t>
+          <t>Sky View Factor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4526,15 +4526,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>SPD = P_road + P_path + P_wall + P_stair + P_pillar, where P_x = pixels_x / total_pixels</t>
+          <t>SVF = (∑_{i=0}^{n} ω · sky(i) / ∑_{i=0}^{n} ω) * 100%</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4544,11 +4544,11 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Sum of the area proportions of elements that divide a coherent and integral activity space within a street-view image; in Zhang et al. (2023) the dividing elements are road, path, wall, stair, and pil</t>
+          <t>Proportion of sky visible from a point</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
@@ -4559,17 +4559,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IND_SQI</t>
+          <t>IND_SVF_CHG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Street Quality Index (Composite)</t>
+          <t>Sky View Factor Change</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SQI = 1.507*GVI + 0.692*SVI + 0.447*EVI - 2.412*MVI - 0.011*SFI - 0.800*PCI - 0.060*VII + 1.414*ITI - 0.167*CCI + 0.208*SWI + 7.798*VEI - 6.344*IRI</t>
+          <t>|SVF_t - SVF_{t-1}|</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>A composite index measuring the overall spatial quality of an urban street based on visual indicators including green view, enclosure, motorization, and openness, derived via AHP weights.</t>
+          <t>The absolute difference in Sky View Factor values between two adjacent measurement points (typically 10m apart).</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -4615,34 +4615,34 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IND_SSVF</t>
+          <t>IND_SVF_DEC</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sign Symbol View Factor</t>
+          <t>Sky View Factor Decrease</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>SSVF = Pixels_sign_symbol / Pixels_total</t>
+          <t>SVFdiff = SVFS - SVFP</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign Symbol View Factor (SSVF): the proportion of pixels classified as 'sign symbol' in a street-view image obtained via semantic segmentation, used as a view-factor measure of pedestrian exposure to </t>
+          <t>The reduction in Sky View Factor attributed to street trees, defined as the difference between the simulation-based building-only SVF (SVFS, computed from a building-height/DSM model) and the photogra</t>
         </is>
       </c>
       <c r="M67" t="n">
@@ -4678,19 +4678,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IND_SVF</t>
+          <t>IND_TER_RAT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sky View Factor</t>
+          <t>Terrain Ratio</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4719,11 +4719,11 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SVF = (∑_{i=0}^{n} ω · sky(i) / ∑_{i=0}^{n} ω) * 100%</t>
+          <t>Terrain_Ratio = N(pixels classified as 'terrain' by SegFormer/Cityscapes) / N(total pixels)</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4733,11 +4733,11 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Proportion of sky visible from a point</t>
+          <t>Proportion of pixels in a street-view image classified as the 'terrain' class under the CityScapes 19-class scheme (bare ground / dirt / sand, distinct from road and sidewalk classes), as estimated by</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
@@ -4748,17 +4748,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IND_SVF_CHG</t>
+          <t>IND_TRF</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sky View Factor Change</t>
+          <t>Traffic Recognition</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>|SVF_t - SVF_{t-1}|</t>
+          <t>TR = (P_traffic_signal + P_sidewalk + P_railway) / P_all</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The absolute difference in Sky View Factor values between two adjacent measurement points (typically 10m apart).</t>
+          <t>The proportion of visual field occupied by traffic guidance elements and pedestrian paths, reflecting safety and recognizability.</t>
         </is>
       </c>
       <c r="M69" t="n">
@@ -4804,24 +4804,24 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IND_SVF_DEC</t>
+          <t>IND_TSV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Sky View Factor Decrease</t>
+          <t>Tree-Sky View Factor</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>component_ratio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>SVFdiff = SVFS - SVFP</t>
+          <t>TVF = Areat / Areas</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>The reduction in Sky View Factor attributed to street trees, defined as the difference between the simulation-based building-only SVF (SVFS, computed from a building-height/DSM model) and the photogra</t>
+          <t>The ratio of plants to the sky in vertical space as seen from a street view image.</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -4867,19 +4867,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IND_TER_RAT</t>
+          <t>IND_TVF</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Terrain Ratio</t>
+          <t>Tree View Factor</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4908,11 +4908,11 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Terrain_Ratio = N(pixels classified as 'terrain' by SegFormer/Cityscapes) / N(total pixels)</t>
+          <t>(Simple) Pixels(Tree) / Total_Pixels  ;  (Hemispherical, Cai et al. 2023) Σ cos(Alti) · Ai · δi,green / Adome,cos</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4922,11 +4922,11 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Proportion of pixels in a street-view image classified as the 'terrain' class under the CityScapes 19-class scheme (bare ground / dirt / sand, distinct from road and sidewalk classes), as estimated by</t>
+          <t>IND_TVF (Tree View Factor) measures the proportion of tree canopy visible from a viewing point. Two operationalizations exist: (1) Simple pixel ratio: Pixels(Tree)/Total_Pixels (commonly used); (2) Co</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
@@ -4937,17 +4937,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IND_TRF</t>
+          <t>IND_TVW</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Traffic Recognition</t>
+          <t>Type of Visual Walkability</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>deep_learning</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>TR = (P_traffic_signal + P_sidewalk + P_railway) / P_all</t>
+          <t>K-means Clustering(Gi, Si, Di, Ni)</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4985,11 +4985,11 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>The proportion of visual field occupied by traffic guidance elements and pedestrian paths, reflecting safety and recognizability.</t>
+          <t>A categorical classification of street segments based on the clustering of visual walkability indicators (greenery, openness, pavement, crowdedness).</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" t="inlineStr">
         <is>
@@ -5000,12 +5000,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IND_TSV</t>
+          <t>IND_VAC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tree-Sky View Factor</t>
+          <t>Visible Accessibility Index</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>component_ratio</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TVF = Areat / Areas</t>
+          <t>Sum(x_perc for x in {sidewalk, escalator, path, stairs, stairway, streetlight, bench, step})</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>The ratio of plants to the sky in vertical space as seen from a street view image.</t>
+          <t>Sum of per-image pixel percentages of accessibility-related PSPNet classes (sidewalk, escalator, path, stairs, stairway, streetlight, bench, step) in a GSV image.</t>
         </is>
       </c>
       <c r="M73" t="n">
@@ -5063,12 +5063,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IND_TVF</t>
+          <t>IND_VEG_DIV</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tree View Factor</t>
+          <t>Vegetation Diversity Index</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5093,15 +5093,15 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>(Simple) Pixels(Tree) / Total_Pixels  ;  (Hemispherical, Cai et al. 2023) Σ cos(Alti) · Ai · δi,green / Adome,cos</t>
+          <t>1 - ((Tn/GVIn)^2 + (Pn/GVIn)^2 + (Gn/GVIn)^2)</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5111,11 +5111,11 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>IND_TVF (Tree View Factor) measures the proportion of tree canopy visible from a viewing point. Two operationalizations exist: (1) Simple pixel ratio: Pixels(Tree)/Total_Pixels (commonly used); (2) Co</t>
+          <t>A measure of the diversity of vegetation types (trees, grass, plants) within the Green View Index, calculated using a Simpson-like index.</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -5126,17 +5126,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IND_TVW</t>
+          <t>IND_VEH</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Type of Visual Walkability</t>
+          <t>Vehicle Ratio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>deep_learning</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5156,15 +5156,15 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>K-means Clustering(Gi, Si, Di, Ni)</t>
+          <t>(Pixels_car + Pixels_truck + Pixels_bus + Pixels_train + Pixels_motorcycle + Pixels_bicycle) / Total_pixels</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>A categorical classification of street segments based on the clustering of visual walkability indicators (greenery, openness, pavement, crowdedness).</t>
+          <t>Proportion of pixels in a street view image classified as motorized/wheeled vehicle categories (car, truck, bus, train, motorcycle, bicycle) under the Cityscapes 19-class scheme.</t>
         </is>
       </c>
       <c r="M75" t="n">
@@ -5189,17 +5189,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IND_VAC</t>
+          <t>IND_VEN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visible Accessibility Index</t>
+          <t>Visual Enclosure</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H76" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Sum(x_perc for x in {sidewalk, escalator, path, stairs, stairway, streetlight, bench, step})</t>
+          <t>VE = (Pixels_building + Pixels_wall + Pixels_tree + Pixels_fence) / Pixels_total · 100%   [exact element list to be confirmed against an authoritative</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Sum of per-image pixel percentages of accessibility-related PSPNet classes (sidewalk, escalator, path, stairs, stairway, streetlight, bench, step) in a GSV image.</t>
+          <t xml:space="preserve">Pixel-area share of vertical, view-bounding elements (buildings, walls, trees, fences) in a street-view image, used as a proxy for the degree of spatial enclosure perceived by a pedestrian (per Yin &amp; </t>
         </is>
       </c>
       <c r="M76" t="n">
@@ -5252,17 +5252,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IND_VEG_DIV</t>
+          <t>IND_VGD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Vegetation Diversity Index</t>
+          <t>Visible Green Distribution</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1 - ((Tn/GVIn)^2 + (Pn/GVIn)^2 + (Gn/GVIn)^2)</t>
+          <t>Spatialclustering_x = 0.5 * (SUM_i SUM_j x_i x_j) / xperc</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>A measure of the diversity of vegetation types (trees, grass, plants) within the Green View Index, calculated using a Simpson-like index.</t>
+          <t xml:space="preserve">A measure of the spatial dispersion/clustering of vegetation pixels within a street-view image, derived as the ratio of joint count statistics over the percent pixel coverage, following Larkin et al. </t>
         </is>
       </c>
       <c r="M77" t="n">
@@ -5315,27 +5315,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IND_VEH</t>
+          <t>IND_VGV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Vehicle Ratio</t>
+          <t>Visual Greenery Vector / Field (VGF)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5345,15 +5345,15 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>(Pixels_car + Pixels_truck + Pixels_bus + Pixels_train + Pixels_motorcycle + Pixels_bicycle) / Total_pixels</t>
+          <t>v_x = GVI_E - GVI_W ; v_y = GVI_N - GVI_S ; |v| = sqrt(v_x^2 + v_y^2) ; theta = atan2(v_y, v_x)  [theta is implicit in the paper but standard]</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5363,11 +5363,11 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Proportion of pixels in a street view image classified as motorized/wheeled vehicle categories (car, truck, bus, train, motorcycle, bicycle) under the Cityscapes 19-class scheme.</t>
+          <t>A 2D vector at each sampling point whose components are signed sums of directional GVI values (north-south on Y; east-west on X), so that the magnitude expresses the strength and the orientation expre</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -5378,22 +5378,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IND_VEN</t>
+          <t>IND_VIB_GRN</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Visual Enclosure</t>
+          <t>Vibrant Green Space</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VE = (Pixels_building + Pixels_wall + Pixels_tree + Pixels_fence) / Pixels_total · 100%   [exact element list to be confirmed against an authoritative</t>
+          <t>VibrantGreen = N(pixels labelled vegetation AND HSV in healthy-green range) / N(total pixels)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixel-area share of vertical, view-bounding elements (buildings, walls, trees, fences) in a street-view image, used as a proxy for the degree of spatial enclosure perceived by a pedestrian (per Yin &amp; </t>
+          <t>Pixel ratio of street-view greenery that also passes a Hue-Saturation-Value (HSV) color filter for 'healthy' green hues. Refines the standard GVI by retaining only pixels that look both vegetative AND</t>
         </is>
       </c>
       <c r="M79" t="n">
@@ -5441,27 +5441,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IND_VGD</t>
+          <t>IND_VII</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Visible Green Distribution</t>
+          <t>Vehicle Interference Index</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Spatialclustering_x = 0.5 * (SUM_i SUM_j x_i x_j) / xperc</t>
+          <t>VII = Pixels_motorised / Pixels_motorway</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t xml:space="preserve">A measure of the spatial dispersion/clustering of vegetation pixels within a street-view image, derived as the ratio of joint count statistics over the percent pixel coverage, following Larkin et al. </t>
+          <t>Ratio of motorised-vehicle pixel area to motorway (carriageway) pixel area within the segmented street-view image, measuring the degree of vehicular intrusion specifically along the carriageway.</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -5504,27 +5504,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IND_VGV</t>
+          <t>IND_VIS_QUA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Visual Greenery Vector / Field (VGF)</t>
+          <t>Visual Quality Index</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CCG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>composite</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>v_x = GVI_E - GVI_W ; v_y = GVI_N - GVI_S ; |v| = sqrt(v_x^2 + v_y^2) ; theta = atan2(v_y, v_x)  [theta is implicit in the paper but standard]</t>
+          <t>VQI = Sum_{k in {Safety, Lively, Beautiful, Wealthy, ...}} score_k   (verify against Wang/Ito/Biljecki 2024 Cities 104704)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>A 2D vector at each sampling point whose components are signed sums of directional GVI values (north-south on Y; east-west on X), so that the magnitude expresses the strength and the orientation expre</t>
+          <t xml:space="preserve">[Re-source from Wang, Z.; Ito, K.; Biljecki, F. 2024 'Assessing the equity and evolution of urban visual perceptual quality with time series street view imagery,' Cities 145, 104704 — that paper, not </t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -5567,12 +5567,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IND_VIB_GRN</t>
+          <t>IND_VPI</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vibrant Green Space</t>
+          <t>Visual Pavement Index</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>two_class_ratio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>VibrantGreen = N(pixels labelled vegetation AND HSV in healthy-green range) / N(total pixels)</t>
+          <t>Pn / (Pn + Rn)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5615,11 +5615,11 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Pixel ratio of street-view greenery that also passes a Hue-Saturation-Value (HSV) color filter for 'healthy' green hues. Refines the standard GVI by retaining only pixels that look both vegetative AND</t>
+          <t>The ratio of visible pavement pixels to the sum of pavement and road pixels, indicating the dominance of pedestrian space relative to vehicle space.</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -5630,27 +5630,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IND_VII</t>
+          <t>IND_VSD</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vehicle Interference Index</t>
+          <t>Vegetation Structural Diversity</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_CFG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>original</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>custom</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>VII = Pixels_motorised / Pixels_motorway</t>
+          <t>VSD = - Sum_{i=1}^{N} p_i * ln(p_i), where p_i = C_i / C_veg</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5678,11 +5678,11 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Ratio of motorised-vehicle pixel area to motorway (carriageway) pixel area within the segmented street-view image, measuring the degree of vehicular intrusion specifically along the carriageway.</t>
+          <t>Vegetation Structural Diversity (VSD): a Shannon-Wiener-based diversity index of the relative pixel proportions of vegetation strata (trees / shrubs / lawns) extracted from semantic segmentation of st</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -5693,17 +5693,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IND_VIS_QUA</t>
+          <t>IND_VSG_BLK</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Visual Quality Index</t>
+          <t>Visible Street Greenery (Block Level)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CAT_CCG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>VQI = Sum_{k in {Safety, Lively, Beautiful, Wealthy, ...}} score_k   (verify against Wang/Ito/Biljecki 2024 Cities 104704)</t>
+          <t>G_n = Σ_i ( G_i · L_i · D_i^α ) / Σ_i ( L_i · D_i^α )   [source: Ye, Xie, Fang, Jiang &amp; Wang 2019; cannot be verified against the supplied PDF for Lon</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Re-source from Wang, Z.; Ito, K.; Biljecki, F. 2024 'Assessing the equity and evolution of urban visual perceptual quality with time series street view imagery,' Cities 145, 104704 — that paper, not </t>
+          <t>Block-level visible street greenery: a length- and distance-weighted aggregate of street-level Green View Index values from streets surrounding (within a buffer of) the block, with a power-law distanc</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -5749,19 +5749,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>future_development</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IND_VPI</t>
+          <t>IND_WAL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Visual Pavement Index</t>
+          <t>Wall Ratio</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>two_class_ratio</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5786,15 +5786,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Pn / (Pn + Rn)</t>
+          <t>Wall Ratio = Pixel_Wall / Total_Pixels</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5804,11 +5804,11 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>The ratio of visible pavement pixels to the sum of pavement and road pixels, indicating the dominance of pedestrian space relative to vehicle space.</t>
+          <t xml:space="preserve">Wall Ratio is the proportion of pixels classified as 'wall' (an ADE-20K class) in a Baidu Street View image after SegNet-based semantic segmentation; reported as the percentage of street element area </t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -5819,17 +5819,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IND_VSD</t>
+          <t>IND_WAT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vegetation Structural Diversity</t>
+          <t>Water View Index</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CAT_CFG</t>
+          <t>CAT_CMP</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>custom</t>
+          <t>ratio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5849,15 +5849,15 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>VSD = - Sum_{i=1}^{N} p_i * ln(p_i), where p_i = C_i / C_veg</t>
+          <t>WVI = Pixels_water / Pixels_total</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5867,11 +5867,11 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Vegetation Structural Diversity (VSD): a Shannon-Wiener-based diversity index of the relative pixel proportions of vegetation strata (trees / shrubs / lawns) extracted from semantic segmentation of st</t>
+          <t xml:space="preserve">Pixel-area proportion of water bodies (rivers, lakes, ponds, sea, fountains) visible in a street-view image, derived from semantic segmentation; used as one of the four/five 'view indexes' (with GVI, </t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -5882,12 +5882,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IND_VSG_BLK</t>
+          <t>IND_WLD</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Visible Street Greenery (Block Level)</t>
+          <t>Wildness</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>composite</t>
+          <t>atan_ratio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>G_n = Σ_i ( G_i · L_i · D_i^α ) / Σ_i ( L_i · D_i^α )   [source: Ye, Xie, Fang, Jiang &amp; Wang 2019; cannot be verified against the supplied PDF for Lon</t>
+          <t>arctan(flora / (grass + non_natural_elements))</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Block-level visible street greenery: a length- and distance-weighted aggregate of street-level Green View Index values from streets surrounding (within a buffer of) the block, with a power-law distanc</t>
+          <t>The inverse tangent of the ratio of flora (bushes/wild nature) to grass and non-natural elements, indicating 'urban wildness' vs generic nature.</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -5938,19 +5938,19 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>future_development</t>
+          <t>active</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IND_WAL</t>
+          <t>IND_WLK_RAT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wall Ratio</t>
+          <t>Visual Walkability Ratio (merged)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ratio</t>
+          <t>two_class_ratio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5975,15 +5975,15 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Wall Ratio = Pixel_Wall / Total_Pixels</t>
+          <t>VisualWalkability = (Sidewalk_pixels + Fence_pixels) / Road_pixels   (equivalently Pavement_pixels + Fence_pixels / Road_pixels under ADE20K-style lab</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5993,11 +5993,11 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wall Ratio is the proportion of pixels classified as 'wall' (an ADE-20K class) in a Baidu Street View image after SegNet-based semantic segmentation; reported as the percentage of street element area </t>
+          <t>Visual walkability ratio of a street view: pixel proportion of pedestrian-oriented surfaces (sidewalk/pavement) plus fence to road pixels, indicating how strongly pedestrian space is visually separate</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -6008,22 +6008,22 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IND_WAT</t>
+          <t>IND_PLD_SHA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Water View Index</t>
+          <t>Plant Diversity — Shannon entropy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CAT_CMP</t>
+          <t>CAT_NAT</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -6042,216 +6042,32 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>WVI = Pixels_water / Pixels_total</t>
+          <t>See calculator_layer_IND_PLD_SHA.py for implementation</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>INCREASE</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>nats or bits (dimensionless)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pixel-area proportion of water bodies (rivers, lakes, ponds, sea, fountains) visible in a street-view image, derived from semantic segmentation; used as one of the four/five 'view indexes' (with GVI, </t>
+          <t>Shannon entropy H' over plant-class proportions.</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>IND_WLD</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Wildness</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CAT_CMP</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>atan_ratio</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>arctan(flora / (grass + non_natural_elements))</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>The inverse tangent of the ratio of flora (bushes/wild nature) to grass and non-natural elements, indicating 'urban wildness' vs generic nature.</t>
-        </is>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>IND_WLK_IDX</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Walkability Index (Visual)</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>CAT_CMP</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>two_class_ratio</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>W_i = ( (1/4) Σ_{j=1..4} P_j + (1/4) Σ_{j=1..4} F_j ) / ( (1/4) Σ_{j=1..4} Road_j )</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Walkability Index (Visual): 在 4 个方向街景图中, 人行道与栅栏像素均值之和占道路像素均值的比值, 衡量街道对步行者的友好程度。</t>
-        </is>
-      </c>
-      <c r="M91" t="n">
-        <v>1</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>IND_WLK_RAT</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Visual Walkability Ratio (merged)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>CAT_CMP</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>original</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>two_class_ratio</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>VisualWalkability = (Sidewalk_pixels + Fence_pixels) / Road_pixels   (equivalently Pavement_pixels + Fence_pixels / Road_pixels under ADE20K-style lab</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Visual walkability ratio of a street view: pixel proportion of pedestrian-oriented surfaces (sidewalk/pavement) plus fence to road pixels, indicating how strongly pedestrian space is visually separate</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
-      </c>
-      <c r="N92" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -6289,7 +6105,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3">
@@ -6299,7 +6115,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -6309,7 +6125,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -6319,7 +6135,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -6329,7 +6145,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -6339,7 +6155,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
